--- a/static/data/exports/Retro_GA_GE_2014.xlsx
+++ b/static/data/exports/Retro_GA_GE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -10559,7 +10559,7 @@
         </is>
       </c>
       <c r="Q163" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R163" t="n">
         <v>21</v>
@@ -11365,7 +11365,7 @@
         </is>
       </c>
       <c r="Q176" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
         <v>21</v>
@@ -12171,7 +12171,7 @@
         </is>
       </c>
       <c r="Q189" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
         <v>21</v>
@@ -12977,7 +12977,7 @@
         </is>
       </c>
       <c r="Q202" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R202" t="n">
         <v>21</v>
@@ -13783,7 +13783,7 @@
         </is>
       </c>
       <c r="Q215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
         <v>21</v>
@@ -14589,7 +14589,7 @@
         </is>
       </c>
       <c r="Q228" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R228" t="n">
         <v>21</v>
@@ -15395,7 +15395,7 @@
         </is>
       </c>
       <c r="Q241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R241" t="n">
         <v>21</v>
@@ -16139,7 +16139,7 @@
         </is>
       </c>
       <c r="Q253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R253" t="n">
         <v>21</v>
@@ -16945,7 +16945,7 @@
         </is>
       </c>
       <c r="Q266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
         <v>21</v>
@@ -17813,7 +17813,7 @@
         </is>
       </c>
       <c r="Q280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R280" t="n">
         <v>21</v>
@@ -18619,7 +18619,7 @@
         </is>
       </c>
       <c r="Q293" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R293" t="n">
         <v>21</v>
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="Q305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R305" t="n">
         <v>21</v>
@@ -20169,7 +20169,7 @@
         </is>
       </c>
       <c r="Q318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R318" t="n">
         <v>21</v>
@@ -20975,7 +20975,7 @@
         </is>
       </c>
       <c r="Q331" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R331" t="n">
         <v>21</v>
@@ -21781,7 +21781,7 @@
         </is>
       </c>
       <c r="Q344" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R344" t="n">
         <v>21</v>
@@ -22649,7 +22649,7 @@
         </is>
       </c>
       <c r="Q358" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R358" t="n">
         <v>21</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="Q371" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R371" t="n">
         <v>21</v>
@@ -24261,7 +24261,7 @@
         </is>
       </c>
       <c r="Q384" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R384" t="n">
         <v>21</v>
@@ -25067,7 +25067,7 @@
         </is>
       </c>
       <c r="Q397" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R397" t="n">
         <v>21</v>
@@ -25873,7 +25873,7 @@
         </is>
       </c>
       <c r="Q410" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R410" t="n">
         <v>21</v>
